--- a/nr-fix-error/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
+++ b/nr-fix-error/ig/StructureDefinition-pdsm-ext-intended-recipient.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-04T12:40:55+00:00</t>
+    <t>2026-03-04T14:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
